--- a/data/merged/2026-09-23/MERGED_US_Spot-Cleaner_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_US_Spot-Cleaner_2026-09-23.xlsx
@@ -3427,13 +3427,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3515,13 +3515,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3691,13 +3691,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3735,13 +3735,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3867,13 +3867,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3911,13 +3911,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3955,13 +3955,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4043,7 +4043,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4093,7 +4093,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4219,13 +4219,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4263,7 +4263,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4313,7 +4313,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4445,7 +4445,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4483,7 +4483,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4527,13 +4527,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4879,13 +4879,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4923,13 +4923,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5055,13 +5055,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5099,13 +5099,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5143,13 +5143,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5187,13 +5187,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5231,13 +5231,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5275,13 +5275,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5474,50 +5474,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6274,7 +6230,7 @@
       <c r="B2" s="13"/>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>B0000DF0RB</t>
+          <t>B00450U6CS</t>
         </is>
       </c>
       <c r="D2" s="14"/>
@@ -6287,23 +6243,23 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>McCulloch MC1275 Heavy-Duty Steam Cleaner, 45 Min Runtime, 18 AccessoriessMop Head, Brushes, &amp; More - Built for Home, Tile,</t>
+          <t>BISSELL Big Green Professional Carpet Cleaner, XL DirtLifter PowerBrushs9-in. long reach hose; 6-in. tough stain tool; BISS</t>
         </is>
       </c>
       <c r="I2" s="14"/>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0000DF0RB?psc=1</t>
+          <t>https://www.amazon.com/dp/B00450U6CS?psc=1</t>
         </is>
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/713yd0dr5iL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61ABtuIJhnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>B0000DF0RB</t>
+          <t>B00450U6CS</t>
         </is>
       </c>
       <c r="M2" s="1"/>
@@ -6320,17 +6276,17 @@
       <c r="X2" s="15"/>
       <c r="Y2"/>
       <c r="Z2" s="19">
-        <v>168.99</v>
+        <v>429</v>
       </c>
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
       <c r="AD2" s="20">
-        <v>15923</v>
+        <v>16589</v>
       </c>
       <c r="AE2"/>
       <c r="AF2" s="21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG2" s="22">
         <v>0</v>
@@ -6382,7 +6338,7 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B00450U6CS</t>
+          <t>B007G1BJNS</t>
         </is>
       </c>
       <c r="D3" s="14"/>
@@ -6395,23 +6351,23 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Big Green Professional Carpet Cleaner, XL DirtLifter PowerBrushs9-in. long reach hose; 6-in. tough stain tool; BISS</t>
+          <t>Bissell Pet Carpet &amp; Upholstery Cleaner, Blue 12oz</t>
         </is>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B00450U6CS?psc=1</t>
+          <t>https://www.amazon.com/dp/B007G1BJNS?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61ABtuIJhnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71UB5YQA-kL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B00450U6CS</t>
+          <t>B007G1BJNS</t>
         </is>
       </c>
       <c r="M3" s="1"/>
@@ -6427,18 +6383,16 @@
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3"/>
-      <c r="Z3" s="19">
-        <v>429</v>
-      </c>
+      <c r="Z3" s="19"/>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3" s="20">
-        <v>16589</v>
+        <v>10582</v>
       </c>
       <c r="AE3"/>
       <c r="AF3" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG3" s="22">
         <v>0</v>
@@ -6490,7 +6444,7 @@
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>B007G1BJNS</t>
+          <t>B009ZJ2M7G</t>
         </is>
       </c>
       <c r="D4" s="14"/>
@@ -6503,23 +6457,23 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>Bissell Pet Carpet &amp; Upholstery Cleaner, Blue 12oz</t>
+          <t>Hoover PowerScrub Deluxe Carpet Cleaner Machine, Pet &amp; Upholstery ToolssDeep Cleaning Carpet Shampooer Machine, SpinScrub B</t>
         </is>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B007G1BJNS?psc=1</t>
+          <t>https://www.amazon.com/dp/B009ZJ2M7G?psc=1</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71UB5YQA-kL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71z52p-4LpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>B007G1BJNS</t>
+          <t>B009ZJ2M7G</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -6535,12 +6489,14 @@
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
       <c r="Y4"/>
-      <c r="Z4" s="19"/>
+      <c r="Z4" s="19">
+        <v>169.99</v>
+      </c>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4" s="20">
-        <v>10582</v>
+        <v>58705</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" s="21">
@@ -6596,7 +6552,7 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B009ZJ2M7G</t>
+          <t>B078YZ586K</t>
         </is>
       </c>
       <c r="D5" s="14"/>
@@ -6609,23 +6565,23 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Hoover PowerScrub Deluxe Carpet Cleaner Machine, Pet &amp; Upholstery ToolssDeep Cleaning Carpet Shampooer Machine, SpinScrub B</t>
+          <t>Hoover PowerDash Pet Compact Carpet Cleaner Machine, Lightweight DesignsHeatForce Fast Drying, Antimicrobial Brush Roll, Pa</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B009ZJ2M7G?psc=1</t>
+          <t>https://www.amazon.com/dp/B078YZ586K?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71z52p-4LpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/713SUK37RZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B009ZJ2M7G</t>
+          <t>B078YZ586K</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -6642,13 +6598,13 @@
       <c r="X5" s="15"/>
       <c r="Y5"/>
       <c r="Z5" s="19">
-        <v>169.99</v>
+        <v>109.99</v>
       </c>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="20">
-        <v>58705</v>
+        <v>82315</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="21">
@@ -6704,7 +6660,7 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B078YZ586K</t>
+          <t>B07DTKXTXV</t>
         </is>
       </c>
       <c r="D6" s="14"/>
@@ -6717,23 +6673,23 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Hoover PowerDash Pet Compact Carpet Cleaner Machine, Lightweight DesignsHeatForce Fast Drying, Antimicrobial Brush Roll, Pa</t>
+          <t>Hoover SmartWash+ Automatic Carpet Cleaner MachinesDeep Cleaning Carpet Shampooer Machine, Pair with a Hoover Carpet Cleane</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B078YZ586K?psc=1</t>
+          <t>https://www.amazon.com/dp/B07DTKXTXV?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/713SUK37RZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71EYr+fsZdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B078YZ586K</t>
+          <t>B07DTKXTXV</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -6750,13 +6706,13 @@
       <c r="X6" s="15"/>
       <c r="Y6"/>
       <c r="Z6" s="19">
-        <v>109.99</v>
+        <v>216.4</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="20">
-        <v>82315</v>
+        <v>21316</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="21">
@@ -6812,7 +6768,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B07DTKXTXV</t>
+          <t>B07QCW1MZX</t>
         </is>
       </c>
       <c r="D7" s="14"/>
@@ -6825,23 +6781,23 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Hoover SmartWash+ Automatic Carpet Cleaner MachinesDeep Cleaning Carpet Shampooer Machine, Pair with a Hoover Carpet Cleane</t>
+          <t>BISSELL Little Green Proheat Portable Deep Cleaner/Spot Cleaner and Car/Auto Detailer with self-Cleaning HydroRinse Tool for</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B07DTKXTXV?psc=1</t>
+          <t>https://www.amazon.com/dp/B07QCW1MZX?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71EYr+fsZdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81tU6kHhJ1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B07DTKXTXV</t>
+          <t>B07QCW1MZX</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -6858,13 +6814,13 @@
       <c r="X7" s="15"/>
       <c r="Y7"/>
       <c r="Z7" s="19">
-        <v>216.4</v>
+        <v>137</v>
       </c>
       <c r="AA7"/>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="20">
-        <v>21316</v>
+        <v>19005</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="21">
@@ -6920,7 +6876,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B07QCW1MZX</t>
+          <t>B085WP2N4Q</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -6933,23 +6889,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Proheat Portable Deep Cleaner/Spot Cleaner and Car/Auto Detailer with self-Cleaning HydroRinse Tool for</t>
+          <t>Hoover SmartWash Pet Automatic Carpet Cleaner Machine with Spot Chaser WandsDeep Cleaning Carpet Shampooer Machine, Pair wi</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B07QCW1MZX?psc=1</t>
+          <t>https://www.amazon.com/dp/B085WP2N4Q?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81tU6kHhJ1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Fkx363LkL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B07QCW1MZX</t>
+          <t>B085WP2N4Q</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6966,13 +6922,13 @@
       <c r="X8" s="15"/>
       <c r="Y8"/>
       <c r="Z8" s="19">
-        <v>137</v>
+        <v>249.99</v>
       </c>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="20">
-        <v>19005</v>
+        <v>8482</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="21">
@@ -7028,7 +6984,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B085WP2N4Q</t>
+          <t>B094Y1HCYK</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -7041,23 +6997,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Hoover SmartWash Pet Automatic Carpet Cleaner Machine with Spot Chaser WandsDeep Cleaning Carpet Shampooer Machine, Pair wi</t>
+          <t>Carpet Cleaner Machine with Deep Cleaning SolutionsPortable Extractor for Couch and Carpet Ideal for Pet home</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B085WP2N4Q?psc=1</t>
+          <t>https://www.amazon.com/dp/B094Y1HCYK?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Fkx363LkL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71BS7sfsgXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B085WP2N4Q</t>
+          <t>B094Y1HCYK</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7074,17 +7030,17 @@
       <c r="X9" s="15"/>
       <c r="Y9"/>
       <c r="Z9" s="19">
-        <v>249.99</v>
+        <v>74.99</v>
       </c>
       <c r="AA9"/>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="20">
-        <v>8482</v>
+        <v>1466</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -7136,7 +7092,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B094Y1HCYK</t>
+          <t>B0B94P5LDK</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7149,23 +7105,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Carpet Cleaner Machine with Deep Cleaning SolutionsPortable Extractor for Couch and Carpet Ideal for Pet home</t>
+          <t>BISSELL ProHeat 2X Revolution Pet Pro Plus Carpet Cleaner, 3588FsDual Dirt Lifter Powerbrush; hose &amp; tool attachment; pet u</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B094Y1HCYK?psc=1</t>
+          <t>https://www.amazon.com/dp/B0B94P5LDK?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71BS7sfsgXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/813lw3gS2vL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B094Y1HCYK</t>
+          <t>B0B94P5LDK</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7182,13 +7138,13 @@
       <c r="X10" s="15"/>
       <c r="Y10"/>
       <c r="Z10" s="19">
-        <v>74.99</v>
+        <v>279.99</v>
       </c>
       <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="20">
-        <v>1466</v>
+        <v>5410</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="21">
@@ -7244,7 +7200,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0B94P5LDK</t>
+          <t>B0BP8GCN87</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7257,23 +7213,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>BISSELL ProHeat 2X Revolution Pet Pro Plus Carpet Cleaner, 3588FsDual Dirt Lifter Powerbrush; hose &amp; tool attachment; pet u</t>
+          <t>BISSELL Revolution HydroSteam Pet Carpet Cleaner, 3432sHydroSteam technology; 2-in-1 pet upholstery tool; cleaning formulas</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0B94P5LDK?psc=1</t>
+          <t>https://www.amazon.com/dp/B0BP8GCN87?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/813lw3gS2vL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81Ic5buE6RL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0B94P5LDK</t>
+          <t>B0BP8GCN87</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7290,17 +7246,17 @@
       <c r="X11" s="15"/>
       <c r="Y11"/>
       <c r="Z11" s="19">
-        <v>279.99</v>
+        <v>399.95</v>
       </c>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="20">
-        <v>5410</v>
+        <v>2230</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
@@ -7352,7 +7308,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0BP8GCN87</t>
+          <t>B0BZDT4LSX</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7365,23 +7321,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Revolution HydroSteam Pet Carpet Cleaner, 3432sHydroSteam technology; 2-in-1 pet upholstery tool; cleaning formulas</t>
+          <t>Dirt Devil Portable Spot Cleaner Machine for Carpet and UpholsterysPowerful Suction Spot Cleaning Machine with Versatile To</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BP8GCN87?psc=1</t>
+          <t>https://www.amazon.com/dp/B0BZDT4LSX?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81Ic5buE6RL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71lAb+SHEmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0BP8GCN87</t>
+          <t>B0BZDT4LSX</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7398,17 +7354,17 @@
       <c r="X12" s="15"/>
       <c r="Y12"/>
       <c r="Z12" s="19">
-        <v>399.95</v>
+        <v>109.99</v>
       </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="20">
-        <v>2230</v>
+        <v>5737</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG12" s="22">
         <v>0</v>
@@ -7460,7 +7416,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0BZDT4LSX</t>
+          <t>B0C1DWP9LK</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7473,23 +7429,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Dirt Devil Portable Spot Cleaner Machine for Carpet and UpholsterysPowerful Suction Spot Cleaning Machine with Versatile To</t>
+          <t>Hoover PowerDash Pet+ Compact Carpet Cleaner, Lightweight Carpet ShampooersHeatforce Faster Drying, Pet Brush Roll, Use wit</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BZDT4LSX?psc=1</t>
+          <t>https://www.amazon.com/dp/B0C1DWP9LK?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71lAb+SHEmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61vXnknHAVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0BZDT4LSX</t>
+          <t>B0C1DWP9LK</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7506,13 +7462,13 @@
       <c r="X13" s="15"/>
       <c r="Y13"/>
       <c r="Z13" s="19">
-        <v>109.99</v>
+        <v>119.99</v>
       </c>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="20">
-        <v>5737</v>
+        <v>1588</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="21">
@@ -7568,7 +7524,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0C1DWP9LK</t>
+          <t>B0C9V4L32W</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7581,23 +7537,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Hoover PowerDash Pet+ Compact Carpet Cleaner, Lightweight Carpet ShampooersHeatforce Faster Drying, Pet Brush Roll, Use wit</t>
+          <t>BISSELL Little Green HydroSteam Portable Carpet Cleaner, 3618sHydroSteam technology combines hot water and steam; multi-pur</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C1DWP9LK?psc=1</t>
+          <t>https://www.amazon.com/dp/B0C9V4L32W?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61vXnknHAVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81LeGewL7iL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0C1DWP9LK</t>
+          <t>B0C9V4L32W</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7613,18 +7569,16 @@
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
       <c r="Y14"/>
-      <c r="Z14" s="19">
-        <v>119.99</v>
-      </c>
+      <c r="Z14" s="19"/>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>1588</v>
+        <v>3816</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
@@ -7676,7 +7630,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0C9V4L32W</t>
+          <t>B0CBNHP6HY</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7689,23 +7643,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green HydroSteam Portable Carpet Cleaner, 3618sHydroSteam technology combines hot water and steam; multi-pur</t>
+          <t>Shark CarpetXpert StainStriker Carpet &amp; Upholstery Cleaner, 3 Tools, EX201sFor Carpet, Upholstery &amp; Rugs, Dirt, Tough Stain</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C9V4L32W?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CBNHP6HY?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81LeGewL7iL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71tB5E-7tTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0C9V4L32W</t>
+          <t>B0CBNHP6HY</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7721,16 +7675,18 @@
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
       <c r="Y15"/>
-      <c r="Z15" s="19"/>
+      <c r="Z15" s="19">
+        <v>249</v>
+      </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="20">
-        <v>3816</v>
+        <v>2846</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -7782,7 +7738,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0CBNHP6HY</t>
+          <t>B0CD9JV7PB</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7795,23 +7751,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetXpert StainStriker Carpet &amp; Upholstery Cleaner, 3 Tools, EX201sFor Carpet, Upholstery &amp; Rugs, Dirt, Tough Stain</t>
+          <t>Hoover CleanSlate XL Deep Cleaning Carpet + Upholstery Spot Cleaner MachinesIncludes Specialized Tools, Permanent Stain Rem</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CBNHP6HY?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CD9JV7PB?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71tB5E-7tTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71-b-jLnUYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0CBNHP6HY</t>
+          <t>B0CD9JV7PB</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7828,17 +7784,17 @@
       <c r="X16" s="15"/>
       <c r="Y16"/>
       <c r="Z16" s="19">
-        <v>249</v>
+        <v>119.99</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="20">
-        <v>2846</v>
+        <v>884</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -7890,7 +7846,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0CD9JV7PB</t>
+          <t>B0CDDJ6P9L</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7903,23 +7859,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Hoover CleanSlate XL Deep Cleaning Carpet + Upholstery Spot Cleaner MachinesIncludes Specialized Tools, Permanent Stain Rem</t>
+          <t>BISSELL TurboClean Pet XL Upright Carpet Cleaner, 3746sUpholstery tough stain tool &amp; formula included; XL capacity for larg</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CD9JV7PB?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CDDJ6P9L?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71-b-jLnUYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/711RS1KI0xL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0CD9JV7PB</t>
+          <t>B0CDDJ6P9L</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7936,17 +7892,17 @@
       <c r="X17" s="15"/>
       <c r="Y17"/>
       <c r="Z17" s="19">
-        <v>119.99</v>
+        <v>179.99</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="20">
-        <v>884</v>
+        <v>4443</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="21">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
@@ -7998,7 +7954,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0CDDJ6P9L</t>
+          <t>B0CS1KZYH5</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -8011,23 +7967,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>BISSELL TurboClean Pet XL Upright Carpet Cleaner, 3746sUpholstery tough stain tool &amp; formula included; XL capacity for larg</t>
+          <t>BISSELL Little Green Max Pet Portable Carpet Cleaner, 3860sSelf-Cleaning Tough Stain Tool &amp; Pet Hair Removal Tool; car/auto</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CDDJ6P9L?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CS1KZYH5?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/711RS1KI0xL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81S23+xZwzL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0CDDJ6P9L</t>
+          <t>B0CS1KZYH5</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8044,17 +8000,17 @@
       <c r="X18" s="15"/>
       <c r="Y18"/>
       <c r="Z18" s="19">
-        <v>179.99</v>
+        <v>109.99</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="20">
-        <v>4443</v>
+        <v>3842</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -8106,7 +8062,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0CS1KZYH5</t>
+          <t>B0CTVWVCPX</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8119,23 +8075,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Max Pet Portable Carpet Cleaner, 3860sSelf-Cleaning Tough Stain Tool &amp; Pet Hair Removal Tool; car/auto</t>
+          <t>Shark EX150 CarpetXpert, Upright Carpet, Area Rug &amp; Upholstery Cleaner for Pets, Built-in Spot &amp; Stain Eliminator, Deep Clean</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CS1KZYH5?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CTVWVCPX?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81S23+xZwzL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61kpNSE-3DL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0CS1KZYH5</t>
+          <t>B0CTVWVCPX</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8152,17 +8108,17 @@
       <c r="X19" s="15"/>
       <c r="Y19"/>
       <c r="Z19" s="19">
-        <v>109.99</v>
+        <v>179.95</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>3842</v>
+        <v>278</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -8214,7 +8170,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0CTVWVCPX</t>
+          <t>B0DC6GDW56</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8227,23 +8183,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Shark EX150 CarpetXpert, Upright Carpet, Area Rug &amp; Upholstery Cleaner for Pets, Built-in Spot &amp; Stain Eliminator, Deep Clean</t>
+          <t>Kenmore Pet Portable Carpet Cleaner Machine with High Cleaning Powers3.2L Clean Tank &amp; 1.4L Dirty Tank, 25ft Cord Length an</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CTVWVCPX?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DC6GDW56?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61kpNSE-3DL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61R71pKMdEL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0CTVWVCPX</t>
+          <t>B0DC6GDW56</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8260,17 +8216,17 @@
       <c r="X20" s="15"/>
       <c r="Y20"/>
       <c r="Z20" s="19">
-        <v>179.95</v>
+        <v>128.99</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>278</v>
+        <v>1309</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -8322,7 +8278,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DC6GDW56</t>
+          <t>B0DDYW1BPQ</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8335,23 +8291,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Kenmore Pet Portable Carpet Cleaner Machine with High Cleaning Powers3.2L Clean Tank &amp; 1.4L Dirty Tank, 25ft Cord Length an</t>
+          <t>Shark CarpetXpert HairPro StainStriker Carpet &amp; Stain Cleaner, EX301sFor Carpet, Upholstery &amp; Rugs, Pet Hair Pickup, Stain</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DC6GDW56?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DDYW1BPQ?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61R71pKMdEL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/810E0dFkkWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DC6GDW56</t>
+          <t>B0DDYW1BPQ</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8368,13 +8324,13 @@
       <c r="X21" s="15"/>
       <c r="Y21"/>
       <c r="Z21" s="19">
-        <v>128.99</v>
+        <v>379</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>1309</v>
+        <v>1001</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
@@ -8430,7 +8386,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0DDYW1BPQ</t>
+          <t>B0DG6LZSLC</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8443,23 +8399,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetXpert HairPro StainStriker Carpet &amp; Stain Cleaner, EX301sFor Carpet, Upholstery &amp; Rugs, Pet Hair Pickup, Stain</t>
+          <t>BISSELL TurboClean PET, Upright Carpet &amp; Upholstery Cleaner, 3948sTurboClean technology for powerful pet hair and stain rem</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DDYW1BPQ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DG6LZSLC?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/810E0dFkkWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71V4Vf4AMSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0DDYW1BPQ</t>
+          <t>B0DG6LZSLC</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8476,17 +8432,17 @@
       <c r="X22" s="15"/>
       <c r="Y22"/>
       <c r="Z22" s="19">
-        <v>379</v>
+        <v>159.99</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>1001</v>
+        <v>3196</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -8538,7 +8494,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0DG6LZSLC</t>
+          <t>B0DJMP6T3N</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8551,23 +8507,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>BISSELL TurboClean PET, Upright Carpet &amp; Upholstery Cleaner, 3948sTurboClean technology for powerful pet hair and stain rem</t>
+          <t>BISSELL Little Green Mini Portable Carpet Cleaner, 4075sHydroRinse self-cleaning tool; 4-in. tough stain tool; upholstery &amp;</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DG6LZSLC?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DJMP6T3N?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71V4Vf4AMSL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Zg+lIkXeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0DG6LZSLC</t>
+          <t>B0DJMP6T3N</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8584,17 +8540,17 @@
       <c r="X23" s="15"/>
       <c r="Y23"/>
       <c r="Z23" s="19">
-        <v>159.99</v>
+        <v>88.99</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>3196</v>
+        <v>10938</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -8646,7 +8602,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0DJMP6T3N</t>
+          <t>B0DM7RXLW7</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8659,23 +8615,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Mini Portable Carpet Cleaner, 4075sHydroRinse self-cleaning tool; 4-in. tough stain tool; upholstery &amp;</t>
+          <t>Armor All SCC301 0901 Upholstery &amp; Carpet Auto Detailing Spot Cleaner</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DJMP6T3N?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DM7RXLW7?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Zg+lIkXeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71bUciIVJrL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0DJMP6T3N</t>
+          <t>B0DM7RXLW7</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8692,17 +8648,17 @@
       <c r="X24" s="15"/>
       <c r="Y24"/>
       <c r="Z24" s="19">
-        <v>88.99</v>
+        <v>79.98</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>10938</v>
+        <v>519</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -8754,7 +8710,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0DM7RXLW7</t>
+          <t>B0DQJTP7SJ</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8767,23 +8723,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Armor All SCC301 0901 Upholstery &amp; Carpet Auto Detailing Spot Cleaner</t>
+          <t>BISSELL Little Green Mini Cordless Portable Carpet Cleaner, 4015sHydroRinse self-cleaning tool; 4-in. tough stain tool; cor</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DM7RXLW7?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DQJTP7SJ?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71bUciIVJrL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71S4MLrY7JL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0DM7RXLW7</t>
+          <t>B0DQJTP7SJ</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8800,17 +8756,17 @@
       <c r="X25" s="15"/>
       <c r="Y25"/>
       <c r="Z25" s="19">
-        <v>79.98</v>
+        <v>89.98</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8862,7 +8818,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0DQJTP7SJ</t>
+          <t>B0FFJ488L9</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8875,23 +8831,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Mini Cordless Portable Carpet Cleaner, 4015sHydroRinse self-cleaning tool; 4-in. tough stain tool; cor</t>
+          <t>Hausmeister Hydroflex Carpet Cleaner Machine, Upholstery Cleaner Machine for Couch, Car Seats &amp; Pet Stains, 500W Powerful Han</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DQJTP7SJ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FFJ488L9?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71S4MLrY7JL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71da0UI9GBL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0DQJTP7SJ</t>
+          <t>B0FFJ488L9</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8908,17 +8864,17 @@
       <c r="X26" s="15"/>
       <c r="Y26"/>
       <c r="Z26" s="19">
-        <v>89.98</v>
+        <v>79.99</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>545</v>
+        <v>176</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8970,7 +8926,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FFJ488L9</t>
+          <t>B0FJBYX36M</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8983,23 +8939,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Hausmeister Hydroflex Carpet Cleaner Machine, Upholstery Cleaner Machine for Couch, Car Seats &amp; Pet Stains, 500W Powerful Han</t>
+          <t>Shark StainStriker Portable Spot &amp; Stain Cleaner, 2 Tools, PX221BRNsFor Carpet, Upholstery &amp; Rugs, Stain &amp; Odor Remover, De</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FFJ488L9?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FJBYX36M?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71da0UI9GBL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Ftd7dp6DL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FFJ488L9</t>
+          <t>B0FJBYX36M</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -9016,17 +8972,17 @@
       <c r="X27" s="15"/>
       <c r="Y27"/>
       <c r="Z27" s="19">
-        <v>79.99</v>
+        <v>139.99</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>176</v>
+        <v>737</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9078,7 +9034,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FJBYX36M</t>
+          <t>B0FLDZGB5D</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9091,23 +9047,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker Portable Spot &amp; Stain Cleaner, 2 Tools, PX221BRNsFor Carpet, Upholstery &amp; Rugs, Stain &amp; Odor Remover, De</t>
+          <t>Shark StainForce Cordless Stain, Odor &amp; Urine Remover, 2 Tools, Caddy HX101sFor Carpets, Area Rugs, Upholstery, Cars &amp; Outd</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FJBYX36M?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FLDZGB5D?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Ftd7dp6DL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71DpEmGZYyL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FJBYX36M</t>
+          <t>B0FLDZGB5D</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9124,17 +9080,17 @@
       <c r="X28" s="15"/>
       <c r="Y28"/>
       <c r="Z28" s="19">
-        <v>139.99</v>
+        <v>199.99</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>737</v>
+        <v>2737</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9186,7 +9142,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FLDZGB5D</t>
+          <t>B0FM86269M</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9199,23 +9155,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Cordless Stain, Odor &amp; Urine Remover, 2 Tools, Caddy HX101sFor Carpets, Area Rugs, Upholstery, Cars &amp; Outd</t>
+          <t>WECLEAN C5 Portable Carpet Cleaner Upholstery Deep Cleaner, Deep Cleaning for Carpet,Car Couch, with Deep Cleaning Solution,B</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FLDZGB5D?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FM86269M?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71DpEmGZYyL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Nhx6AdN9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FLDZGB5D</t>
+          <t>B0FM86269M</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9232,17 +9188,17 @@
       <c r="X29" s="15"/>
       <c r="Y29"/>
       <c r="Z29" s="19">
-        <v>199.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>2737</v>
+        <v>227</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -9294,7 +9250,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FM86269M</t>
+          <t>B0G1MTJNC9</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9307,23 +9263,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>WECLEAN C5 Portable Carpet Cleaner Upholstery Deep Cleaner, Deep Cleaning for Carpet,Car Couch, with Deep Cleaning Solution,B</t>
+          <t>Rivenara Carpet Cleaner Machine Upholstery - 450W Shampooer Couch Cleaning Portable Vacuum Rug Sofa Car Seat Fabric Mattress</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FM86269M?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G1MTJNC9?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Nhx6AdN9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/517qkqp5raL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FM86269M</t>
+          <t>B0G1MTJNC9</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9340,13 +9296,13 @@
       <c r="X30" s="15"/>
       <c r="Y30"/>
       <c r="Z30" s="19">
-        <v>65.99</v>
+        <v>49.48</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>227</v>
+        <v>863</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
@@ -9402,7 +9358,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0G1MTJNC9</t>
+          <t>B0GD55G5Y9</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9415,23 +9371,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Rivenara Carpet Cleaner Machine Upholstery - 450W Shampooer Couch Cleaning Portable Vacuum Rug Sofa Car Seat Fabric Mattress</t>
+          <t>Starrybot Portable Carpet Cleaner with Steam, 18Kpa Spot Cleaner(Gray)sSteam and heating technology help lift pet messes, c</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G1MTJNC9?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GD55G5Y9?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/517qkqp5raL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0G1MTJNC9</t>
+          <t>B0GD55G5Y9</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9448,17 +9404,17 @@
       <c r="X31" s="15"/>
       <c r="Y31"/>
       <c r="Z31" s="19">
-        <v>49.48</v>
+        <v>99.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>863</v>
+        <v>1266</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -9510,7 +9466,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GD55G5Y9</t>
+          <t>B0GD5JVBPG</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9523,23 +9479,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Starrybot Portable Carpet Cleaner with Steam, 18Kpa Spot Cleaner(Gray)sSteam and heating technology help lift pet messes, c</t>
+          <t>Starrybot Upholstery Cleaner Machine, 18Kpa Pet Stain Extractor(white)sPortable spot cleaner for carpets, sofas, car interi</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GD55G5Y9?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GD5JVBPG?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71uWJC4R3yL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GD55G5Y9</t>
+          <t>B0GD5JVBPG</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9556,13 +9512,13 @@
       <c r="X32" s="15"/>
       <c r="Y32"/>
       <c r="Z32" s="19">
-        <v>99.99</v>
+        <v>62.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="20">
-        <v>1266</v>
+        <v>1443</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="21">
@@ -9618,7 +9574,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GD5JVBPG</t>
+          <t>B0GHMZ4YJB</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9631,23 +9587,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Starrybot Upholstery Cleaner Machine, 18Kpa Pet Stain Extractor(white)sPortable spot cleaner for carpets, sofas, car interi</t>
+          <t>DREAME N20 Steam Carpet Cleaner Machine with Steam &amp; Hot Water WashsPortable Upholstery Cleaner with Self Cleaning, 17Kpa S</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GD5JVBPG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GHMZ4YJB?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71uWJC4R3yL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71QxLRlJCdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GD5JVBPG</t>
+          <t>B0GHMZ4YJB</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9664,17 +9620,17 @@
       <c r="X33" s="15"/>
       <c r="Y33"/>
       <c r="Z33" s="19">
-        <v>62.99</v>
+        <v>159.99</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>1443</v>
+        <v>394</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -9726,7 +9682,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GHMZ4YJB</t>
+          <t>B0GNTQQH68</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9739,23 +9695,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>DREAME N20 Steam Carpet Cleaner Machine with Steam &amp; Hot Water WashsPortable Upholstery Cleaner with Self Cleaning, 17Kpa S</t>
+          <t>BISSELL Little Green Multi-Purpose Portable Carpet Cleaner, 3353DsExclusive specialty tools; car &amp; auto detailing; Amazon E</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GHMZ4YJB?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GNTQQH68?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71QxLRlJCdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71ATOBDN26L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GHMZ4YJB</t>
+          <t>B0GNTQQH68</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9771,14 +9727,12 @@
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
       <c r="Y34"/>
-      <c r="Z34" s="19">
-        <v>159.99</v>
-      </c>
+      <c r="Z34" s="19"/>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="20">
-        <v>394</v>
+        <v>175</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="21">
@@ -9834,7 +9788,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GNTQQH68</t>
+          <t>B0GRKCTL66</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9847,23 +9801,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Multi-Purpose Portable Carpet Cleaner, 3353DsExclusive specialty tools; car &amp; auto detailing; Amazon E</t>
+          <t>Rosewill Multi-Purpose Portable Carpet and Upholstery Cleaner, Powerful Suction 17 KPa Spot Cleaner, 550W Motor, Car and Auto</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GNTQQH68?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GRKCTL66?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71ATOBDN26L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71NLGCprGML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GNTQQH68</t>
+          <t>B0GRKCTL66</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9879,16 +9833,18 @@
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35"/>
-      <c r="Z35" s="19"/>
+      <c r="Z35" s="19">
+        <v>59.97</v>
+      </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
@@ -9940,7 +9896,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GRKCTL66</t>
+          <t>B0GV18GWQ3</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9953,23 +9909,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Rosewill Multi-Purpose Portable Carpet and Upholstery Cleaner, Powerful Suction 17 KPa Spot Cleaner, 550W Motor, Car and Auto</t>
+          <t>Shark StainForce Cordless Portable Spot, Stain, &amp; Odor Remover System for Carpets, Area Rugs, Upholstery, Stairs, with Storag</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GRKCTL66?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GV18GWQ3?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71NLGCprGML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71u4dii+k+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GRKCTL66</t>
+          <t>B0GV18GWQ3</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9986,17 +9942,17 @@
       <c r="X36" s="15"/>
       <c r="Y36"/>
       <c r="Z36" s="19">
-        <v>59.97</v>
+        <v>89</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="20">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="21">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AG36" s="22">
         <v>0</v>
@@ -10048,7 +10004,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GV18GWQ3</t>
+          <t>B0H1G4S2W6</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10061,23 +10017,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Cordless Portable Spot, Stain, &amp; Odor Remover System for Carpets, Area Rugs, Upholstery, Stairs, with Storag</t>
+          <t>Uwant Carpet Cleaner Machine 18Kpa Portable Carpet Cleaner for Cars Couch, 2in1 Water Tank Upholstery Cleaner, Spot Cleaner w</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GV18GWQ3?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H1G4S2W6?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71u4dii+k+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81S5HuBNRsL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GV18GWQ3</t>
+          <t>B0H1G4S2W6</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10094,17 +10050,17 @@
       <c r="X37" s="15"/>
       <c r="Y37"/>
       <c r="Z37" s="19">
-        <v>89</v>
+        <v>69.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="20">
-        <v>34</v>
+        <v>476</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="21">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
@@ -10156,7 +10112,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0H1G4S2W6</t>
+          <t>B0H2F9PHDG</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10169,23 +10125,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Uwant Carpet Cleaner Machine 18Kpa Portable Carpet Cleaner for Cars Couch, 2in1 Water Tank Upholstery Cleaner, Spot Cleaner w</t>
+          <t>Ailltopd Portable Carpet &amp; Upholstery Spot Cleaner Machine, 15Kpa Powerful Suction &amp; Couch Cleaner, Deep Cleaning for Carpet,</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H1G4S2W6?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H2F9PHDG?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81S5HuBNRsL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71v+MhOT86L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0H1G4S2W6</t>
+          <t>B0H2F9PHDG</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10202,17 +10158,17 @@
       <c r="X38" s="15"/>
       <c r="Y38"/>
       <c r="Z38" s="19">
-        <v>69.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="20">
-        <v>476</v>
+        <v>63</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="21">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
@@ -10264,7 +10220,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0H2F9PHDG</t>
+          <t>B0H2K8JSC3</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10277,23 +10233,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Ailltopd Portable Carpet &amp; Upholstery Spot Cleaner Machine, 15Kpa Powerful Suction &amp; Couch Cleaner, Deep Cleaning for Carpet,</t>
+          <t>Shark CarpetForce HairPro Lightweight Upright Carpet &amp; Rug Cleaner, EX551sFor Carpets &amp; Area Rugs, Lightweight, Two Modes,</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H2F9PHDG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H2K8JSC3?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71v+MhOT86L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71OjyPFG33L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0H2F9PHDG</t>
+          <t>B0H2K8JSC3</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10310,17 +10266,17 @@
       <c r="X39" s="15"/>
       <c r="Y39"/>
       <c r="Z39" s="19">
-        <v>89.99</v>
+        <v>229.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="20">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="21">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -10372,7 +10328,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0H2K8JSC3</t>
+          <t>B0H39MT1KV</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10385,23 +10341,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetForce HairPro Lightweight Upright Carpet &amp; Rug Cleaner, EX551sFor Carpets &amp; Area Rugs, Lightweight, Two Modes,</t>
+          <t>Kenmore SpotLite Go Pet Portable Carpet &amp; Upholstery Cleaner Machines16KPa Suction with 2-in-1 Tough Stain Tool, Lightweigh</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H2K8JSC3?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H39MT1KV?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71OjyPFG33L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71MsbgI3HYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0H2K8JSC3</t>
+          <t>B0H39MT1KV</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10418,17 +10374,17 @@
       <c r="X40" s="15"/>
       <c r="Y40"/>
       <c r="Z40" s="19">
-        <v>229.99</v>
+        <v>73.79</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="20">
-        <v>92</v>
+        <v>3304</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -10480,7 +10436,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0H39MT1KV</t>
+          <t>B0H3T9MSFL</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10493,23 +10449,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Kenmore SpotLite Go Pet Portable Carpet &amp; Upholstery Cleaner Machines16KPa Suction with 2-in-1 Tough Stain Tool, Lightweigh</t>
+          <t>Uwant 18Kpa Upholstery Cleaner Machine with Pet Pro Cleaner&amp;Tools Set of 1sPortable Carpet Cleaner with 3 Brush Heads for C</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H39MT1KV?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H3T9MSFL?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71MsbgI3HYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71FHK5YalsL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0H39MT1KV</t>
+          <t>B0H3T9MSFL</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10526,17 +10482,17 @@
       <c r="X41" s="15"/>
       <c r="Y41"/>
       <c r="Z41" s="19">
-        <v>73.79</v>
+        <v>69.95</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="20">
-        <v>3304</v>
+        <v>848</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="21">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
@@ -10588,7 +10544,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0H3T9MSFL</t>
+          <t>B0H4QNFHK7</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10601,23 +10557,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Uwant 18Kpa Upholstery Cleaner Machine with Pet Pro Cleaner&amp;Tools Set of 1sPortable Carpet Cleaner with 3 Brush Heads for C</t>
+          <t>Portable Carpet &amp; Upholstery Cleaner Machine, 21kPa Spot Cleaner MachinesHandheld Furniture Shampooer Deep Cleaning for Cou</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H3T9MSFL?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H4QNFHK7?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71FHK5YalsL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71EAW1f9taL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0H3T9MSFL</t>
+          <t>B0H4QNFHK7</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10634,13 +10590,13 @@
       <c r="X42" s="15"/>
       <c r="Y42"/>
       <c r="Z42" s="19">
-        <v>69.95</v>
+        <v>99.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="20">
-        <v>848</v>
+        <v>26</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="21">
@@ -10696,7 +10652,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H4QNFHK7</t>
+          <t>B0H5PMDTZ9</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10709,23 +10665,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Portable Carpet &amp; Upholstery Cleaner Machine, 21kPa Spot Cleaner MachinesHandheld Furniture Shampooer Deep Cleaning for Cou</t>
+          <t>Vacmaster 30 Series Mini Portable Carpet &amp; Upholstery Spot Cleaner Machines16KPa Power Suction includes tough stain tool an</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H4QNFHK7?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H5PMDTZ9?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71EAW1f9taL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Aw9FoxdML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H4QNFHK7</t>
+          <t>B0H5PMDTZ9</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10742,17 +10698,17 @@
       <c r="X43" s="15"/>
       <c r="Y43"/>
       <c r="Z43" s="19">
-        <v>99.99</v>
+        <v>61.59</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="20">
-        <v>26</v>
+        <v>2867</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="22">
         <v>0</v>
@@ -10804,7 +10760,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H5PMDTZ9</t>
+          <t>B0H838PW81</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10817,23 +10773,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster 30 Series Mini Portable Carpet &amp; Upholstery Spot Cleaner Machines16KPa Power Suction includes tough stain tool an</t>
+          <t>Portable Spot Cleaner Machine for Carpet and Upholstery - 15Kpa Deep Spot Cleaning for Area Rugs, Pets, Car, Couch Cleaner Ma</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H5PMDTZ9?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H838PW81?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Aw9FoxdML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71t4zcpGClL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H5PMDTZ9</t>
+          <t>B0H838PW81</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10850,17 +10806,17 @@
       <c r="X44" s="15"/>
       <c r="Y44"/>
       <c r="Z44" s="19">
-        <v>61.59</v>
+        <v>89.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="20">
-        <v>2867</v>
+        <v>301</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG44" s="22">
         <v>0</v>
@@ -10912,7 +10868,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H838PW81</t>
+          <t>B0H8NP2VTJ</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10925,23 +10881,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Portable Spot Cleaner Machine for Carpet and Upholstery - 15Kpa Deep Spot Cleaning for Area Rugs, Pets, Car, Couch Cleaner Ma</t>
+          <t>NEWBULIG Carpet and Upholstery Cleaner Machine Portable Carpet ShampooersCouch Cleaner with 3 Brushes, Removable Water Tank</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H838PW81?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H8NP2VTJ?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71t4zcpGClL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/719sTT52W2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H838PW81</t>
+          <t>B0H8NP2VTJ</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10958,17 +10914,17 @@
       <c r="X45" s="15"/>
       <c r="Y45"/>
       <c r="Z45" s="19">
-        <v>89.99</v>
+        <v>45.48</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="20">
-        <v>301</v>
+        <v>23</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="21">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
@@ -11020,7 +10976,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0H8NP2VTJ</t>
+          <t>B0HBBW3K99</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -11033,23 +10989,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>NEWBULIG Carpet and Upholstery Cleaner Machine Portable Carpet ShampooersCouch Cleaner with 3 Brushes, Removable Water Tank</t>
+          <t>PUREBEAR 18Kpa Portable HandHeld Carpet Cleaner Machine With ShampooersSpot Cleaner| Upholstery, Furniture| Couch, Car Seat</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H8NP2VTJ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HBBW3K99?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/719sTT52W2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0H8NP2VTJ</t>
+          <t>B0HBBW3K99</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11066,17 +11022,17 @@
       <c r="X46" s="15"/>
       <c r="Y46"/>
       <c r="Z46" s="19">
-        <v>45.48</v>
+        <v>94.1</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="20">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="21">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
@@ -11128,7 +11084,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0HBBW3K99</t>
+          <t>B0HFGC7KJM</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11141,23 +11097,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR 18Kpa Portable HandHeld Carpet Cleaner Machine With ShampooersSpot Cleaner| Upholstery, Furniture| Couch, Car Seat</t>
+          <t>OLIXIS Carpet Cleaner Machine Upholstery Couch Cleaner Solution Portables3 Brushes, Spot Shampooer, Dual Removable Water Ta</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HBBW3K99?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HFGC7KJM?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71xBI-0uegL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0HBBW3K99</t>
+          <t>B0HFGC7KJM</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11174,17 +11130,17 @@
       <c r="X47" s="15"/>
       <c r="Y47"/>
       <c r="Z47" s="19">
-        <v>94.1</v>
+        <v>45.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="20">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="21">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -11236,7 +11192,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0HFGC7KJM</t>
+          <t>B0HFLXXLQW</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11249,23 +11205,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>OLIXIS Carpet Cleaner Machine Upholstery Couch Cleaner Solution Portables3 Brushes, Spot Shampooer, Dual Removable Water Ta</t>
+          <t>Uwant Portable Carpet Cleaner with Steam&amp; Hot Water 18Kpa Upholstery Cleaner Machine for Pets with Cleaning Tools&amp; Solution C</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HFGC7KJM?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HFLXXLQW?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71xBI-0uegL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71f8WWuJ-2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0HFGC7KJM</t>
+          <t>B0HFLXXLQW</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11282,17 +11238,17 @@
       <c r="X48" s="15"/>
       <c r="Y48"/>
       <c r="Z48" s="19">
-        <v>45.99</v>
+        <v>129.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="20">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="21">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
@@ -11344,7 +11300,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0HFLXXLQW</t>
+          <t>B0HGXLKPNX</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11357,23 +11313,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Uwant Portable Carpet Cleaner with Steam&amp; Hot Water 18Kpa Upholstery Cleaner Machine for Pets with Cleaning Tools&amp; Solution C</t>
+          <t>Yoomie Portable Carpet Cleaner &amp; Upholstery Cleaner Machine - 21Kpa Carpet Cleaner Machine, Self-Cleaning, Deep Cleaner for P</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HFLXXLQW?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HGXLKPNX?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71f8WWuJ-2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71p-BhyALsL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0HFLXXLQW</t>
+          <t>B0HGXLKPNX</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11390,13 +11346,13 @@
       <c r="X49" s="15"/>
       <c r="Y49"/>
       <c r="Z49" s="19">
-        <v>129.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="20">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="21">
@@ -11452,7 +11408,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0HGXLKPNX</t>
+          <t>B0HH9SLYX5</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -11465,23 +11421,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Yoomie Portable Carpet Cleaner &amp; Upholstery Cleaner Machine - 21Kpa Carpet Cleaner Machine, Self-Cleaning, Deep Cleaner for P</t>
+          <t>Uwant Carpet Cleaner Machine with Steam&amp;Hot&amp;Cold Water System 18Kpa Powerful Suction Upholstery Cleaner Machine with Pet Pro</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HGXLKPNX?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HH9SLYX5?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71p-BhyALsL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Ow7RgFT9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0HGXLKPNX</t>
+          <t>B0HH9SLYX5</t>
         </is>
       </c>
       <c r="M50" s="1"/>
@@ -11498,13 +11454,13 @@
       <c r="X50" s="15"/>
       <c r="Y50"/>
       <c r="Z50" s="19">
-        <v>99.99</v>
+        <v>169.99</v>
       </c>
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50"/>
       <c r="AD50" s="20">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="AE50"/>
       <c r="AF50" s="21">
@@ -11553,370 +11509,257 @@
       <c r="BQ50" s="23"/>
       <c r="BR50"/>
     </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HH9SLYX5</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.comundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Uwant Carpet Cleaner Machine with Steam&amp;Hot&amp;Cold Water System 18Kpa Powerful Suction Upholstery Cleaner Machine with Pet Pro</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HH9SLYX5?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Ow7RgFT9L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HH9SLYX5</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="19">
-        <v>169.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="20">
-        <v>56</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="20"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="20"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.com/dp/B0000DF0RB"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.com/dp/B00450U6CS"/>
     <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.com/dp/B0000DF0RB?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/713yd0dr5iL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.com/dp/B0000DF0RB"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.com/dp/B00450U6CS"/>
+    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.com/dp/B00450U6CS?psc=1"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ABtuIJhnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.com/dp/B00450U6CS"/>
+    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.com/dp/B007G1BJNS"/>
     <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.com/dp/B00450U6CS?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ABtuIJhnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.com/dp/B00450U6CS"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.com/dp/B007G1BJNS"/>
+    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.com/dp/B007G1BJNS?psc=1"/>
+    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-na.ssl-images-amazon.com/images/I/71UB5YQA-kL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.com/dp/B007G1BJNS"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.com/dp/B009ZJ2M7G"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.com/dp/B007G1BJNS?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-na.ssl-images-amazon.com/images/I/71UB5YQA-kL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.com/dp/B007G1BJNS"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.com/dp/B009ZJ2M7G"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.com/dp/B009ZJ2M7G?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-na.ssl-images-amazon.com/images/I/71z52p-4LpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.com/dp/B009ZJ2M7G"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.com/dp/B078YZ586K"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.com/dp/B009ZJ2M7G?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/71z52p-4LpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.com/dp/B009ZJ2M7G"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.com/dp/B078YZ586K"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.com/dp/B078YZ586K?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/713SUK37RZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.com/dp/B078YZ586K"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.com/dp/B07DTKXTXV"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.com/dp/B078YZ586K?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-na.ssl-images-amazon.com/images/I/713SUK37RZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.com/dp/B078YZ586K"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.com/dp/B07DTKXTXV"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.com/dp/B07DTKXTXV?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-na.ssl-images-amazon.com/images/I/71EYr+fsZdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.com/dp/B07DTKXTXV"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.com/dp/B07QCW1MZX"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.com/dp/B07DTKXTXV?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-na.ssl-images-amazon.com/images/I/71EYr+fsZdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.com/dp/B07DTKXTXV"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.com/dp/B07QCW1MZX"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.com/dp/B07QCW1MZX?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-na.ssl-images-amazon.com/images/I/81tU6kHhJ1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.com/dp/B07QCW1MZX"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.com/dp/B085WP2N4Q"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.com/dp/B07QCW1MZX?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-na.ssl-images-amazon.com/images/I/81tU6kHhJ1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.com/dp/B07QCW1MZX"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.com/dp/B085WP2N4Q"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.com/dp/B085WP2N4Q?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Fkx363LkL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.com/dp/B085WP2N4Q"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.com/dp/B094Y1HCYK"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.com/dp/B085WP2N4Q?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Fkx363LkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.com/dp/B085WP2N4Q"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.com/dp/B094Y1HCYK"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.com/dp/B094Y1HCYK?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/71BS7sfsgXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.com/dp/B094Y1HCYK"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.com/dp/B0B94P5LDK"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.com/dp/B094Y1HCYK?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-na.ssl-images-amazon.com/images/I/71BS7sfsgXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.com/dp/B094Y1HCYK"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.com/dp/B0B94P5LDK"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.com/dp/B0B94P5LDK?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-na.ssl-images-amazon.com/images/I/813lw3gS2vL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.com/dp/B0B94P5LDK"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.com/dp/B0BP8GCN87"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.com/dp/B0B94P5LDK?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/813lw3gS2vL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.com/dp/B0B94P5LDK"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.com/dp/B0BP8GCN87"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.com/dp/B0BP8GCN87?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Ic5buE6RL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.com/dp/B0BP8GCN87"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.com/dp/B0BZDT4LSX"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.com/dp/B0BP8GCN87?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Ic5buE6RL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.com/dp/B0BP8GCN87"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.com/dp/B0BZDT4LSX"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.com/dp/B0BZDT4LSX?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lAb+SHEmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.com/dp/B0BZDT4LSX"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.com/dp/B0C1DWP9LK"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.com/dp/B0BZDT4LSX?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lAb+SHEmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.com/dp/B0BZDT4LSX"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.com/dp/B0C1DWP9LK"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.com/dp/B0C1DWP9LK?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-na.ssl-images-amazon.com/images/I/61vXnknHAVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.com/dp/B0C1DWP9LK"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.com/dp/B0C9V4L32W"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.com/dp/B0C1DWP9LK?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-na.ssl-images-amazon.com/images/I/61vXnknHAVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.com/dp/B0C1DWP9LK"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.com/dp/B0C9V4L32W"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.com/dp/B0C9V4L32W?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-na.ssl-images-amazon.com/images/I/81LeGewL7iL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.com/dp/B0C9V4L32W"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.com/dp/B0CBNHP6HY"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.com/dp/B0C9V4L32W?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-na.ssl-images-amazon.com/images/I/81LeGewL7iL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.com/dp/B0C9V4L32W"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.com/dp/B0CBNHP6HY"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.com/dp/B0CBNHP6HY?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-na.ssl-images-amazon.com/images/I/71tB5E-7tTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.com/dp/B0CBNHP6HY"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.com/dp/B0CD9JV7PB"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.com/dp/B0CBNHP6HY?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-na.ssl-images-amazon.com/images/I/71tB5E-7tTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.com/dp/B0CBNHP6HY"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.com/dp/B0CD9JV7PB"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.com/dp/B0CD9JV7PB?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-na.ssl-images-amazon.com/images/I/71-b-jLnUYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.com/dp/B0CD9JV7PB"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.com/dp/B0CDDJ6P9L"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.com/dp/B0CD9JV7PB?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-na.ssl-images-amazon.com/images/I/71-b-jLnUYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.com/dp/B0CD9JV7PB"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.com/dp/B0CDDJ6P9L"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.com/dp/B0CDDJ6P9L?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-na.ssl-images-amazon.com/images/I/711RS1KI0xL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.com/dp/B0CDDJ6P9L"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.com/dp/B0CS1KZYH5"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.com/dp/B0CDDJ6P9L?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/711RS1KI0xL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.com/dp/B0CDDJ6P9L"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.com/dp/B0CS1KZYH5"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.com/dp/B0CS1KZYH5?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/81S23+xZwzL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.com/dp/B0CS1KZYH5"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.com/dp/B0CTVWVCPX"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.com/dp/B0CS1KZYH5?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/81S23+xZwzL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.com/dp/B0CS1KZYH5"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.com/dp/B0CTVWVCPX"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.com/dp/B0CTVWVCPX?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/61kpNSE-3DL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.com/dp/B0CTVWVCPX"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.com/dp/B0DC6GDW56"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.com/dp/B0CTVWVCPX?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-na.ssl-images-amazon.com/images/I/61kpNSE-3DL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.com/dp/B0CTVWVCPX"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.com/dp/B0DC6GDW56"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.com/dp/B0DC6GDW56?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-na.ssl-images-amazon.com/images/I/61R71pKMdEL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.com/dp/B0DC6GDW56"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.com/dp/B0DDYW1BPQ"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.com/dp/B0DC6GDW56?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/61R71pKMdEL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.com/dp/B0DC6GDW56"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.com/dp/B0DDYW1BPQ"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.com/dp/B0DDYW1BPQ?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/810E0dFkkWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.com/dp/B0DDYW1BPQ"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.com/dp/B0DG6LZSLC"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.com/dp/B0DDYW1BPQ?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/810E0dFkkWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.com/dp/B0DDYW1BPQ"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.com/dp/B0DG6LZSLC"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.com/dp/B0DG6LZSLC?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/71V4Vf4AMSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.com/dp/B0DG6LZSLC"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.com/dp/B0DJMP6T3N"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.com/dp/B0DG6LZSLC?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-na.ssl-images-amazon.com/images/I/71V4Vf4AMSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.com/dp/B0DG6LZSLC"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.com/dp/B0DJMP6T3N"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.com/dp/B0DJMP6T3N?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Zg+lIkXeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.com/dp/B0DJMP6T3N"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.com/dp/B0DM7RXLW7"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.com/dp/B0DJMP6T3N?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Zg+lIkXeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.com/dp/B0DJMP6T3N"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.com/dp/B0DM7RXLW7"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.com/dp/B0DM7RXLW7?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/71bUciIVJrL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.com/dp/B0DM7RXLW7"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.com/dp/B0DQJTP7SJ"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.com/dp/B0DM7RXLW7?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-na.ssl-images-amazon.com/images/I/71bUciIVJrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.com/dp/B0DM7RXLW7"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.com/dp/B0DQJTP7SJ"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.com/dp/B0DQJTP7SJ?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-na.ssl-images-amazon.com/images/I/71S4MLrY7JL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.com/dp/B0DQJTP7SJ"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.com/dp/B0FFJ488L9"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.com/dp/B0DQJTP7SJ?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-na.ssl-images-amazon.com/images/I/71S4MLrY7JL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.com/dp/B0DQJTP7SJ"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.com/dp/B0FFJ488L9"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.com/dp/B0FFJ488L9?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-na.ssl-images-amazon.com/images/I/71da0UI9GBL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.com/dp/B0FFJ488L9"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.com/dp/B0FJBYX36M"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.com/dp/B0FFJ488L9?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-na.ssl-images-amazon.com/images/I/71da0UI9GBL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.com/dp/B0FFJ488L9"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.com/dp/B0FJBYX36M"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.com/dp/B0FJBYX36M?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Ftd7dp6DL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.com/dp/B0FJBYX36M"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.com/dp/B0FLDZGB5D"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.com/dp/B0FJBYX36M?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Ftd7dp6DL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.com/dp/B0FJBYX36M"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.com/dp/B0FLDZGB5D"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.com/dp/B0FLDZGB5D?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-na.ssl-images-amazon.com/images/I/71DpEmGZYyL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.com/dp/B0FLDZGB5D"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.com/dp/B0FM86269M"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.com/dp/B0FLDZGB5D?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-na.ssl-images-amazon.com/images/I/71DpEmGZYyL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.com/dp/B0FLDZGB5D"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.com/dp/B0FM86269M"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.com/dp/B0FM86269M?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Nhx6AdN9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.com/dp/B0FM86269M"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.com/dp/B0G1MTJNC9"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.com/dp/B0FM86269M?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Nhx6AdN9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.com/dp/B0FM86269M"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.com/dp/B0G1MTJNC9"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.com/dp/B0G1MTJNC9?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-na.ssl-images-amazon.com/images/I/517qkqp5raL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.com/dp/B0G1MTJNC9"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.com/dp/B0GD55G5Y9"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.com/dp/B0G1MTJNC9?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/517qkqp5raL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.com/dp/B0G1MTJNC9"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.com/dp/B0GD55G5Y9"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.com/dp/B0GD55G5Y9?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.com/dp/B0GD55G5Y9"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.com/dp/B0GD5JVBPG"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.com/dp/B0GD55G5Y9?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.com/dp/B0GD55G5Y9"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.com/dp/B0GD5JVBPG"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.com/dp/B0GD5JVBPG?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/71uWJC4R3yL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.com/dp/B0GD5JVBPG"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.com/dp/B0GHMZ4YJB"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.com/dp/B0GD5JVBPG?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-na.ssl-images-amazon.com/images/I/71uWJC4R3yL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.com/dp/B0GD5JVBPG"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.com/dp/B0GHMZ4YJB"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.com/dp/B0GHMZ4YJB?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-na.ssl-images-amazon.com/images/I/71QxLRlJCdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.com/dp/B0GHMZ4YJB"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.com/dp/B0GNTQQH68"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.com/dp/B0GHMZ4YJB?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-na.ssl-images-amazon.com/images/I/71QxLRlJCdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.com/dp/B0GHMZ4YJB"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.com/dp/B0GNTQQH68"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.com/dp/B0GNTQQH68?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ATOBDN26L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.com/dp/B0GNTQQH68"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.com/dp/B0GRKCTL66"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.com/dp/B0GNTQQH68?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ATOBDN26L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.com/dp/B0GNTQQH68"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.com/dp/B0GRKCTL66"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.com/dp/B0GRKCTL66?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NLGCprGML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.com/dp/B0GRKCTL66"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.com/dp/B0GV18GWQ3"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.com/dp/B0GRKCTL66?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NLGCprGML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.com/dp/B0GRKCTL66"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.com/dp/B0GV18GWQ3"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.com/dp/B0GV18GWQ3?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/71u4dii+k+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.com/dp/B0GV18GWQ3"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.com/dp/B0H1G4S2W6"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.com/dp/B0GV18GWQ3?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/71u4dii+k+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.com/dp/B0GV18GWQ3"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.com/dp/B0H1G4S2W6"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.com/dp/B0H1G4S2W6?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/81S5HuBNRsL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.com/dp/B0H1G4S2W6"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.com/dp/B0H2F9PHDG"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.com/dp/B0H1G4S2W6?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/81S5HuBNRsL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.com/dp/B0H1G4S2W6"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.com/dp/B0H2F9PHDG"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.com/dp/B0H2F9PHDG?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/71v+MhOT86L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.com/dp/B0H2F9PHDG"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.com/dp/B0H2K8JSC3"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.com/dp/B0H2F9PHDG?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-na.ssl-images-amazon.com/images/I/71v+MhOT86L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.com/dp/B0H2F9PHDG"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.com/dp/B0H2K8JSC3"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.com/dp/B0H2K8JSC3?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OjyPFG33L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.com/dp/B0H2K8JSC3"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.com/dp/B0H39MT1KV"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.com/dp/B0H2K8JSC3?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OjyPFG33L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.com/dp/B0H2K8JSC3"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.com/dp/B0H39MT1KV"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.com/dp/B0H39MT1KV?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/71MsbgI3HYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.com/dp/B0H39MT1KV"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.com/dp/B0H3T9MSFL"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.com/dp/B0H39MT1KV?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/71MsbgI3HYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.com/dp/B0H39MT1KV"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.com/dp/B0H3T9MSFL"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.com/dp/B0H3T9MSFL?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/71FHK5YalsL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.com/dp/B0H3T9MSFL"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.com/dp/B0H4QNFHK7"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.com/dp/B0H3T9MSFL?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-na.ssl-images-amazon.com/images/I/71FHK5YalsL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.com/dp/B0H3T9MSFL"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.com/dp/B0H4QNFHK7"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.com/dp/B0H4QNFHK7?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-na.ssl-images-amazon.com/images/I/71EAW1f9taL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.com/dp/B0H4QNFHK7"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.com/dp/B0H5PMDTZ9"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.com/dp/B0H4QNFHK7?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/71EAW1f9taL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.com/dp/B0H4QNFHK7"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.com/dp/B0H5PMDTZ9"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.com/dp/B0H5PMDTZ9?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Aw9FoxdML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.com/dp/B0H5PMDTZ9"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.com/dp/B0H838PW81"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.com/dp/B0H5PMDTZ9?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Aw9FoxdML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.com/dp/B0H5PMDTZ9"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.com/dp/B0H838PW81"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.com/dp/B0H838PW81?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71t4zcpGClL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.com/dp/B0H838PW81"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.com/dp/B0H8NP2VTJ"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.com/dp/B0H838PW81?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/71t4zcpGClL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.com/dp/B0H838PW81"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.com/dp/B0H8NP2VTJ"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.com/dp/B0H8NP2VTJ?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/719sTT52W2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.com/dp/B0H8NP2VTJ"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.com/dp/B0HBBW3K99"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.com/dp/B0H8NP2VTJ?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/719sTT52W2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.com/dp/B0H8NP2VTJ"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.com/dp/B0HBBW3K99"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.com/dp/B0HBBW3K99?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.com/dp/B0HBBW3K99"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.com/dp/B0HFGC7KJM"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.com/dp/B0HBBW3K99?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.com/dp/B0HBBW3K99"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.com/dp/B0HFGC7KJM"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.com/dp/B0HFGC7KJM?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xBI-0uegL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.com/dp/B0HFGC7KJM"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.com/dp/B0HFLXXLQW"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.com/dp/B0HFGC7KJM?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xBI-0uegL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.com/dp/B0HFGC7KJM"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.com/dp/B0HFLXXLQW"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.com/dp/B0HFLXXLQW?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-na.ssl-images-amazon.com/images/I/71f8WWuJ-2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.com/dp/B0HFLXXLQW"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.com/dp/B0HGXLKPNX"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.com/dp/B0HFLXXLQW?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/71f8WWuJ-2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.com/dp/B0HFLXXLQW"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.com/dp/B0HGXLKPNX"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.com/dp/B0HGXLKPNX?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p-BhyALsL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.com/dp/B0HGXLKPNX"/>
+    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.com/dp/B0HH9SLYX5"/>
     <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.com/dp/B0HGXLKPNX?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p-BhyALsL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.com/dp/B0HGXLKPNX"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.com/dp/B0HH9SLYX5"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.com/dp/B0HH9SLYX5?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Ow7RgFT9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.com/dp/B0HH9SLYX5"/>
+    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.com/dp/B0HH9SLYX5?psc=1"/>
+    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Ow7RgFT9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.com/dp/B0HH9SLYX5"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
